--- a/artfynd/A 5450-2023 artfynd.xlsx
+++ b/artfynd/A 5450-2023 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113071538</v>
+        <v>113071539</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622067</v>
+        <v>621958</v>
       </c>
       <c r="R4" t="n">
-        <v>7214387</v>
+        <v>7214367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113071539</v>
+        <v>113071538</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621958</v>
+        <v>622067</v>
       </c>
       <c r="R5" t="n">
-        <v>7214367</v>
+        <v>7214387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5450-2023 artfynd.xlsx
+++ b/artfynd/A 5450-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5450-2023 artfynd.xlsx
+++ b/artfynd/A 5450-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,108 +1129,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>113951337</v>
-      </c>
-      <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Gunnarn, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>622131</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7214408</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
